--- a/examples/Full_mwtab_example/NMR/extract/NMR_colon_measurements.xlsx
+++ b/examples/Full_mwtab_example/NMR/extract/NMR_colon_measurements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sparda\Desktop\Moseley Lab\Code\MESSES\examples\Full_mwtab_example\NMR\extract\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sparda\Desktop\Moseley Lab\Code\MESSES_main\MESSES\examples\Full_mwtab_example\NMR\extract\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F24293-6B12-4225-A12A-654BE7762EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8D0499E-700A-4C7A-9E0B-04A5B54D12B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4215" yWindow="1140" windowWidth="21720" windowHeight="12975" activeTab="2" xr2:uid="{432708A5-97B1-49E8-8A1C-5E278420EF0F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{432708A5-97B1-49E8-8A1C-5E278420EF0F}"/>
   </bookViews>
   <sheets>
     <sheet name="#automate" sheetId="3" r:id="rId1"/>
@@ -1647,9 +1647,6 @@
     <t>#.chemical_shift_ref_cpd</t>
   </si>
   <si>
-    <t>#.temperature;#%units=celsius</t>
-  </si>
-  <si>
     <t>#.acquisition_time;#%units=s</t>
   </si>
   <si>
@@ -1720,9 +1717,6 @@
   </si>
   <si>
     <t>#measurement.intensity;#%type="normalized peak area"</t>
-  </si>
-  <si>
-    <t>#measurement.transient_peak;#%type="integer"</t>
   </si>
   <si>
     <t>#unique=false</t>
@@ -1932,13 +1926,19 @@
     <t>assignment method</t>
   </si>
   <si>
-    <t>#measurement.assignment%method.assign</t>
-  </si>
-  <si>
     <t>database</t>
   </si>
   <si>
     <t>#measurement.compound.assign</t>
+  </si>
+  <si>
+    <t>#measurement.transient_peak;#.transient_peak_type="integer"</t>
+  </si>
+  <si>
+    <t>#measurement.assignment_method.assign</t>
+  </si>
+  <si>
+    <t>#.temperature;#%units=C</t>
   </si>
 </sst>
 </file>
@@ -2016,9 +2016,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2056,7 +2056,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2162,7 +2162,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2304,7 +2304,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2370,42 +2370,42 @@
         <v>533</v>
       </c>
       <c r="Q2" t="s">
+        <v>631</v>
+      </c>
+      <c r="R2" t="s">
         <v>534</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>535</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>536</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>537</v>
       </c>
-      <c r="U2" t="s">
-        <v>538</v>
-      </c>
       <c r="V2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="W2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D3" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E3" t="s">
+        <v>540</v>
+      </c>
+      <c r="F3" t="s">
+        <v>540</v>
+      </c>
+      <c r="G3" t="s">
         <v>541</v>
-      </c>
-      <c r="F3" t="s">
-        <v>541</v>
-      </c>
-      <c r="G3" t="s">
-        <v>542</v>
       </c>
       <c r="H3">
         <v>0.5</v>
@@ -2414,22 +2414,22 @@
         <v>600</v>
       </c>
       <c r="J3" t="s">
+        <v>542</v>
+      </c>
+      <c r="K3" t="s">
         <v>543</v>
-      </c>
-      <c r="K3" t="s">
-        <v>544</v>
       </c>
       <c r="L3">
         <v>1.7</v>
       </c>
       <c r="M3" t="s">
+        <v>544</v>
+      </c>
+      <c r="N3" t="s">
         <v>545</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>546</v>
-      </c>
-      <c r="O3" t="s">
-        <v>547</v>
       </c>
       <c r="P3" t="s">
         <v>7</v>
@@ -2444,16 +2444,16 @@
         <v>4</v>
       </c>
       <c r="T3" t="s">
+        <v>547</v>
+      </c>
+      <c r="U3" t="s">
         <v>548</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>549</v>
       </c>
-      <c r="V3" t="s">
-        <v>550</v>
-      </c>
       <c r="W3" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
@@ -2464,175 +2464,175 @@
         <v>520</v>
       </c>
       <c r="D5" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E5" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D6" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E6" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D7" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E7" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D8" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E8" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D9" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E9" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D10" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E10" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D11" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E11" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D12" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E12" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D13" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="E13" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D14" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E14" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D15" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E15" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D16" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E16" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D17" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E17" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D18" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E18" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D19" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E19" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D20" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E20" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -2653,7 +2653,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D26" t="s">
         <v>127</v>
@@ -2664,7 +2664,7 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -2672,7 +2672,7 @@
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2680,7 +2680,7 @@
         <v>2</v>
       </c>
       <c r="D29" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2696,7 +2696,7 @@
         <v>3</v>
       </c>
       <c r="D31" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -2704,7 +2704,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
@@ -2712,20 +2712,20 @@
         <v>5</v>
       </c>
       <c r="D33" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D34" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D35" t="s">
         <v>128</v>
@@ -2733,7 +2733,7 @@
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D36" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
   </sheetData>
@@ -2773,7 +2773,7 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -74056,19 +74056,19 @@
         <v>123</v>
       </c>
       <c r="B1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C1" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="D1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
@@ -74079,7 +74079,7 @@
         <v>203</v>
       </c>
       <c r="D2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
@@ -74090,7 +74090,7 @@
         <v>209</v>
       </c>
       <c r="D3" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
@@ -74101,7 +74101,7 @@
         <v>171</v>
       </c>
       <c r="D4" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -74112,7 +74112,7 @@
         <v>177</v>
       </c>
       <c r="D5" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -74123,29 +74123,29 @@
         <v>340</v>
       </c>
       <c r="D6" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C7" t="s">
         <v>171</v>
       </c>
       <c r="D7" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C8" t="s">
         <v>177</v>
       </c>
       <c r="D8" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
@@ -74156,7 +74156,7 @@
         <v>409</v>
       </c>
       <c r="D9" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -74164,19 +74164,19 @@
         <v>123</v>
       </c>
       <c r="B12" t="s">
+        <v>575</v>
+      </c>
+      <c r="C12" t="s">
+        <v>576</v>
+      </c>
+      <c r="F12" t="s">
         <v>577</v>
       </c>
-      <c r="C12" t="s">
-        <v>578</v>
-      </c>
-      <c r="F12" t="s">
-        <v>579</v>
-      </c>
       <c r="L12" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="M12" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
@@ -74184,10 +74184,10 @@
         <v>105</v>
       </c>
       <c r="C13" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F13" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="S13" t="str">
         <f>_xlfn.CONCAT("r'",B13,"',r'",C13,"'")</f>
@@ -74199,10 +74199,10 @@
         <v>108</v>
       </c>
       <c r="C14" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="F14" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="S14" t="str">
         <f t="shared" ref="S14:S27" si="0">_xlfn.CONCAT("r'",B14,"',r'",C14,"'")</f>
@@ -74214,10 +74214,10 @@
         <v>109</v>
       </c>
       <c r="C15" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="F15" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="S15" t="str">
         <f t="shared" si="0"/>
@@ -74229,10 +74229,10 @@
         <v>110</v>
       </c>
       <c r="C16" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="F16" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="S16" t="str">
         <f t="shared" si="0"/>
@@ -74244,10 +74244,10 @@
         <v>111</v>
       </c>
       <c r="C17" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="F17" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="S17" t="str">
         <f t="shared" si="0"/>
@@ -74259,10 +74259,10 @@
         <v>112</v>
       </c>
       <c r="C18" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="F18" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="S18" t="str">
         <f t="shared" si="0"/>
@@ -74274,10 +74274,10 @@
         <v>113</v>
       </c>
       <c r="C19" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F19" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="S19" t="str">
         <f t="shared" si="0"/>
@@ -74289,10 +74289,10 @@
         <v>114</v>
       </c>
       <c r="C20" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="F20" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="S20" t="str">
         <f t="shared" si="0"/>
@@ -74304,10 +74304,10 @@
         <v>115</v>
       </c>
       <c r="C21" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F21" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="S21" t="str">
         <f t="shared" si="0"/>
@@ -74319,10 +74319,10 @@
         <v>116</v>
       </c>
       <c r="C22" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F22" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="S22" t="str">
         <f t="shared" si="0"/>
@@ -74334,10 +74334,10 @@
         <v>117</v>
       </c>
       <c r="C23" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F23" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="S23" t="str">
         <f t="shared" si="0"/>
@@ -74349,10 +74349,10 @@
         <v>118</v>
       </c>
       <c r="C24" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="F24" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="S24" t="str">
         <f t="shared" si="0"/>
@@ -74364,10 +74364,10 @@
         <v>119</v>
       </c>
       <c r="C25" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="F25" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="S25" t="str">
         <f t="shared" si="0"/>
@@ -74379,10 +74379,10 @@
         <v>120</v>
       </c>
       <c r="C26" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="F26" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="S26" t="str">
         <f t="shared" si="0"/>
@@ -74394,10 +74394,10 @@
         <v>121</v>
       </c>
       <c r="C27" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F27" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="S27" t="str">
         <f t="shared" si="0"/>
@@ -74419,7 +74419,7 @@
         <v>123</v>
       </c>
       <c r="B1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E1" t="s">
         <v>514</v>
@@ -74428,7 +74428,7 @@
         <v>515</v>
       </c>
       <c r="J1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="K1" t="s">
         <v>516</v>
@@ -74443,10 +74443,10 @@
         <v>519</v>
       </c>
       <c r="P1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="Q1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -74475,7 +74475,7 @@
         <v>137</v>
       </c>
       <c r="J2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="K2" t="s">
         <v>138</v>
@@ -74513,7 +74513,7 @@
         <v>142</v>
       </c>
       <c r="J3" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K3" t="s">
         <v>143</v>
@@ -74551,7 +74551,7 @@
         <v>147</v>
       </c>
       <c r="J4" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K4" t="s">
         <v>148</v>
@@ -74589,7 +74589,7 @@
         <v>147</v>
       </c>
       <c r="J5" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K5" t="s">
         <v>152</v>
@@ -74627,7 +74627,7 @@
         <v>156</v>
       </c>
       <c r="J6" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K6" t="s">
         <v>157</v>
@@ -74665,7 +74665,7 @@
         <v>147</v>
       </c>
       <c r="J7" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K7" t="s">
         <v>160</v>
@@ -74703,7 +74703,7 @@
         <v>156</v>
       </c>
       <c r="J8" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K8" t="s">
         <v>162</v>
@@ -74741,7 +74741,7 @@
         <v>156</v>
       </c>
       <c r="J9" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K9" t="s">
         <v>157</v>
@@ -74779,7 +74779,7 @@
         <v>147</v>
       </c>
       <c r="J10" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K10" t="s">
         <v>160</v>
@@ -74817,7 +74817,7 @@
         <v>156</v>
       </c>
       <c r="J11" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K11" t="s">
         <v>162</v>
@@ -74855,7 +74855,7 @@
         <v>167</v>
       </c>
       <c r="J12" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K12" t="s">
         <v>168</v>
@@ -74893,7 +74893,7 @@
         <v>172</v>
       </c>
       <c r="J13" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K13" t="s">
         <v>173</v>
@@ -74931,7 +74931,7 @@
         <v>172</v>
       </c>
       <c r="J14" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K14" t="s">
         <v>173</v>
@@ -74969,7 +74969,7 @@
         <v>167</v>
       </c>
       <c r="J15" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K15" t="s">
         <v>178</v>
@@ -75007,7 +75007,7 @@
         <v>172</v>
       </c>
       <c r="J16" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K16" t="s">
         <v>182</v>
@@ -75045,7 +75045,7 @@
         <v>172</v>
       </c>
       <c r="J17" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K17" t="s">
         <v>187</v>
@@ -75083,7 +75083,7 @@
         <v>167</v>
       </c>
       <c r="J18" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K18" t="s">
         <v>191</v>
@@ -75121,7 +75121,7 @@
         <v>172</v>
       </c>
       <c r="J19" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K19" t="s">
         <v>194</v>
@@ -75159,7 +75159,7 @@
         <v>167</v>
       </c>
       <c r="J20" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K20" t="s">
         <v>196</v>
@@ -75197,7 +75197,7 @@
         <v>156</v>
       </c>
       <c r="J21" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K21" t="s">
         <v>199</v>
@@ -75235,7 +75235,7 @@
         <v>172</v>
       </c>
       <c r="J22" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K22" t="s">
         <v>201</v>
@@ -75273,7 +75273,7 @@
         <v>204</v>
       </c>
       <c r="J23" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K23" t="s">
         <v>205</v>
@@ -75311,7 +75311,7 @@
         <v>204</v>
       </c>
       <c r="J24" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K24" t="s">
         <v>205</v>
@@ -75349,7 +75349,7 @@
         <v>210</v>
       </c>
       <c r="J25" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K25" t="s">
         <v>211</v>
@@ -75387,7 +75387,7 @@
         <v>167</v>
       </c>
       <c r="J26" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K26" t="s">
         <v>178</v>
@@ -75425,7 +75425,7 @@
         <v>167</v>
       </c>
       <c r="J27" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K27" t="s">
         <v>217</v>
@@ -75463,7 +75463,7 @@
         <v>172</v>
       </c>
       <c r="J28" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K28" t="s">
         <v>220</v>
@@ -75501,7 +75501,7 @@
         <v>167</v>
       </c>
       <c r="J29" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K29" t="s">
         <v>224</v>
@@ -75539,7 +75539,7 @@
         <v>167</v>
       </c>
       <c r="J30" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K30" t="s">
         <v>143</v>
@@ -75577,7 +75577,7 @@
         <v>210</v>
       </c>
       <c r="J31" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K31" t="s">
         <v>229</v>
@@ -75615,7 +75615,7 @@
         <v>210</v>
       </c>
       <c r="J32" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K32" t="s">
         <v>233</v>
@@ -75650,7 +75650,7 @@
         <v>204</v>
       </c>
       <c r="J33" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K33" t="s">
         <v>234</v>
@@ -75688,7 +75688,7 @@
         <v>167</v>
       </c>
       <c r="J34" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K34" t="s">
         <v>237</v>
@@ -75726,7 +75726,7 @@
         <v>167</v>
       </c>
       <c r="J35" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K35" t="s">
         <v>241</v>
@@ -75764,7 +75764,7 @@
         <v>210</v>
       </c>
       <c r="J36" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K36" t="s">
         <v>245</v>
@@ -75799,7 +75799,7 @@
         <v>210</v>
       </c>
       <c r="J37" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K37" t="s">
         <v>249</v>
@@ -75837,7 +75837,7 @@
         <v>251</v>
       </c>
       <c r="J38" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K38" t="s">
         <v>252</v>
@@ -75875,7 +75875,7 @@
         <v>172</v>
       </c>
       <c r="J39" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K39" t="s">
         <v>253</v>
@@ -75913,7 +75913,7 @@
         <v>147</v>
       </c>
       <c r="J40" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K40" t="s">
         <v>255</v>
@@ -75951,7 +75951,7 @@
         <v>210</v>
       </c>
       <c r="J41" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K41" t="s">
         <v>259</v>
@@ -75989,7 +75989,7 @@
         <v>147</v>
       </c>
       <c r="J42" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K42" t="s">
         <v>260</v>
@@ -76027,7 +76027,7 @@
         <v>204</v>
       </c>
       <c r="J43" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K43" t="s">
         <v>263</v>
@@ -76065,7 +76065,7 @@
         <v>147</v>
       </c>
       <c r="J44" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K44" t="s">
         <v>255</v>
@@ -76103,7 +76103,7 @@
         <v>172</v>
       </c>
       <c r="J45" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K45" t="s">
         <v>255</v>
@@ -76141,7 +76141,7 @@
         <v>147</v>
       </c>
       <c r="J46" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K46" t="s">
         <v>260</v>
@@ -76179,7 +76179,7 @@
         <v>172</v>
       </c>
       <c r="J47" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K47" t="s">
         <v>270</v>
@@ -76217,7 +76217,7 @@
         <v>172</v>
       </c>
       <c r="J48" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K48" t="s">
         <v>255</v>
@@ -76255,7 +76255,7 @@
         <v>172</v>
       </c>
       <c r="J49" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K49" t="s">
         <v>274</v>
@@ -76293,7 +76293,7 @@
         <v>167</v>
       </c>
       <c r="J50" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K50" t="s">
         <v>277</v>
@@ -76331,7 +76331,7 @@
         <v>204</v>
       </c>
       <c r="J51" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K51" t="s">
         <v>279</v>
@@ -76369,7 +76369,7 @@
         <v>172</v>
       </c>
       <c r="J52" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K52" t="s">
         <v>270</v>
@@ -76407,7 +76407,7 @@
         <v>204</v>
       </c>
       <c r="J53" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K53" t="s">
         <v>279</v>
@@ -76445,7 +76445,7 @@
         <v>204</v>
       </c>
       <c r="J54" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K54" t="s">
         <v>286</v>
@@ -76483,7 +76483,7 @@
         <v>204</v>
       </c>
       <c r="J55" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K55" t="s">
         <v>286</v>
@@ -76521,7 +76521,7 @@
         <v>172</v>
       </c>
       <c r="J56" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K56" t="s">
         <v>294</v>
@@ -76559,7 +76559,7 @@
         <v>167</v>
       </c>
       <c r="J57" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K57" t="s">
         <v>277</v>
@@ -76597,7 +76597,7 @@
         <v>172</v>
       </c>
       <c r="J58" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K58" t="s">
         <v>299</v>
@@ -76635,7 +76635,7 @@
         <v>172</v>
       </c>
       <c r="J59" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K59" t="s">
         <v>303</v>
@@ -76673,7 +76673,7 @@
         <v>147</v>
       </c>
       <c r="J60" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K60" t="s">
         <v>305</v>
@@ -76711,7 +76711,7 @@
         <v>147</v>
       </c>
       <c r="J61" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K61" t="s">
         <v>307</v>
@@ -76749,7 +76749,7 @@
         <v>172</v>
       </c>
       <c r="J62" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K62" t="s">
         <v>310</v>
@@ -76787,7 +76787,7 @@
         <v>147</v>
       </c>
       <c r="J63" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K63" t="s">
         <v>314</v>
@@ -76825,7 +76825,7 @@
         <v>147</v>
       </c>
       <c r="J64" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K64" t="s">
         <v>316</v>
@@ -76863,7 +76863,7 @@
         <v>172</v>
       </c>
       <c r="J65" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K65" t="s">
         <v>294</v>
@@ -76901,7 +76901,7 @@
         <v>147</v>
       </c>
       <c r="J66" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K66" t="s">
         <v>318</v>
@@ -76939,7 +76939,7 @@
         <v>172</v>
       </c>
       <c r="J67" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K67" t="s">
         <v>299</v>
@@ -76977,7 +76977,7 @@
         <v>172</v>
       </c>
       <c r="J68" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K68" t="s">
         <v>303</v>
@@ -77015,7 +77015,7 @@
         <v>172</v>
       </c>
       <c r="J69" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K69" t="s">
         <v>310</v>
@@ -77053,7 +77053,7 @@
         <v>147</v>
       </c>
       <c r="J70" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K70" t="s">
         <v>320</v>
@@ -77091,7 +77091,7 @@
         <v>167</v>
       </c>
       <c r="J71" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K71" t="s">
         <v>323</v>
@@ -77129,7 +77129,7 @@
         <v>147</v>
       </c>
       <c r="J72" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K72" t="s">
         <v>320</v>
@@ -77167,7 +77167,7 @@
         <v>147</v>
       </c>
       <c r="J73" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K73" t="s">
         <v>325</v>
@@ -77205,7 +77205,7 @@
         <v>167</v>
       </c>
       <c r="J74" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K74" t="s">
         <v>329</v>
@@ -77243,7 +77243,7 @@
         <v>147</v>
       </c>
       <c r="J75" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K75" t="s">
         <v>333</v>
@@ -77281,7 +77281,7 @@
         <v>147</v>
       </c>
       <c r="J76" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K76" t="s">
         <v>334</v>
@@ -77319,7 +77319,7 @@
         <v>210</v>
       </c>
       <c r="J77" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K77" t="s">
         <v>338</v>
@@ -77357,7 +77357,7 @@
         <v>147</v>
       </c>
       <c r="J78" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K78" t="s">
         <v>341</v>
@@ -77395,7 +77395,7 @@
         <v>156</v>
       </c>
       <c r="J79" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K79" t="s">
         <v>345</v>
@@ -77433,7 +77433,7 @@
         <v>147</v>
       </c>
       <c r="J80" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K80" t="s">
         <v>349</v>
@@ -77471,7 +77471,7 @@
         <v>167</v>
       </c>
       <c r="J81" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K81" t="s">
         <v>351</v>
@@ -77509,7 +77509,7 @@
         <v>172</v>
       </c>
       <c r="J82" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K82" t="s">
         <v>353</v>
@@ -77547,7 +77547,7 @@
         <v>147</v>
       </c>
       <c r="J83" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K83" t="s">
         <v>355</v>
@@ -77585,7 +77585,7 @@
         <v>172</v>
       </c>
       <c r="J84" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K84" t="s">
         <v>353</v>
@@ -77623,7 +77623,7 @@
         <v>147</v>
       </c>
       <c r="J85" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K85" t="s">
         <v>355</v>
@@ -77661,7 +77661,7 @@
         <v>167</v>
       </c>
       <c r="J86" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K86" t="s">
         <v>360</v>
@@ -77699,7 +77699,7 @@
         <v>167</v>
       </c>
       <c r="J87" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K87" t="s">
         <v>362</v>
@@ -77737,7 +77737,7 @@
         <v>167</v>
       </c>
       <c r="J88" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K88" t="s">
         <v>365</v>
@@ -77775,7 +77775,7 @@
         <v>204</v>
       </c>
       <c r="J89" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K89" t="s">
         <v>367</v>
@@ -77813,7 +77813,7 @@
         <v>147</v>
       </c>
       <c r="J90" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K90" t="s">
         <v>370</v>
@@ -77851,7 +77851,7 @@
         <v>147</v>
       </c>
       <c r="J91" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K91" t="s">
         <v>372</v>
@@ -77889,7 +77889,7 @@
         <v>147</v>
       </c>
       <c r="J92" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K92" t="s">
         <v>374</v>
@@ -77927,7 +77927,7 @@
         <v>147</v>
       </c>
       <c r="J93" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K93" t="s">
         <v>378</v>
@@ -77965,7 +77965,7 @@
         <v>167</v>
       </c>
       <c r="J94" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K94" t="s">
         <v>380</v>
@@ -78003,7 +78003,7 @@
         <v>167</v>
       </c>
       <c r="J95" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K95" t="s">
         <v>382</v>
@@ -78041,7 +78041,7 @@
         <v>385</v>
       </c>
       <c r="J96" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K96" t="s">
         <v>386</v>
@@ -78079,7 +78079,7 @@
         <v>167</v>
       </c>
       <c r="J97" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K97" t="s">
         <v>391</v>
@@ -78117,7 +78117,7 @@
         <v>172</v>
       </c>
       <c r="J98" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K98" t="s">
         <v>393</v>
@@ -78155,7 +78155,7 @@
         <v>167</v>
       </c>
       <c r="J99" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K99" t="s">
         <v>396</v>
@@ -78193,7 +78193,7 @@
         <v>167</v>
       </c>
       <c r="J100" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K100" t="s">
         <v>400</v>
@@ -78231,7 +78231,7 @@
         <v>167</v>
       </c>
       <c r="J101" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K101" t="s">
         <v>404</v>
@@ -78269,7 +78269,7 @@
         <v>210</v>
       </c>
       <c r="J102" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K102" t="s">
         <v>407</v>
@@ -78307,7 +78307,7 @@
         <v>147</v>
       </c>
       <c r="J103" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K103" t="s">
         <v>410</v>
@@ -78345,7 +78345,7 @@
         <v>167</v>
       </c>
       <c r="J104" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K104" t="s">
         <v>415</v>
@@ -78383,7 +78383,7 @@
         <v>167</v>
       </c>
       <c r="J105" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K105" t="s">
         <v>418</v>
@@ -78421,7 +78421,7 @@
         <v>147</v>
       </c>
       <c r="J106" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K106" t="s">
         <v>420</v>
@@ -78459,7 +78459,7 @@
         <v>147</v>
       </c>
       <c r="J107" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K107" t="s">
         <v>420</v>
@@ -78497,7 +78497,7 @@
         <v>167</v>
       </c>
       <c r="J108" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K108" t="s">
         <v>424</v>
@@ -78535,7 +78535,7 @@
         <v>167</v>
       </c>
       <c r="J109" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K109" t="s">
         <v>428</v>
@@ -78578,7 +78578,7 @@
         <v>204</v>
       </c>
       <c r="J111" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K111" t="s">
         <v>432</v>
@@ -78616,7 +78616,7 @@
         <v>147</v>
       </c>
       <c r="J112" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K112" t="s">
         <v>436</v>
@@ -78654,7 +78654,7 @@
         <v>147</v>
       </c>
       <c r="J113" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K113" t="s">
         <v>157</v>
@@ -78692,7 +78692,7 @@
         <v>156</v>
       </c>
       <c r="J114" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K114" t="s">
         <v>442</v>
@@ -78730,7 +78730,7 @@
         <v>172</v>
       </c>
       <c r="J115" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K115" t="s">
         <v>444</v>
@@ -78768,7 +78768,7 @@
         <v>172</v>
       </c>
       <c r="J116" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K116" t="s">
         <v>444</v>
@@ -78806,7 +78806,7 @@
         <v>172</v>
       </c>
       <c r="J117" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K117" t="s">
         <v>444</v>
@@ -78849,7 +78849,7 @@
         <v>204</v>
       </c>
       <c r="J119" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K119" t="s">
         <v>451</v>
@@ -78887,7 +78887,7 @@
         <v>172</v>
       </c>
       <c r="J120" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K120" t="s">
         <v>456</v>
@@ -78922,7 +78922,7 @@
         <v>225</v>
       </c>
       <c r="J121" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K121" t="s">
         <v>456</v>
@@ -78960,7 +78960,7 @@
         <v>461</v>
       </c>
       <c r="J122" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K122" t="s">
         <v>462</v>
@@ -78995,7 +78995,7 @@
         <v>94</v>
       </c>
       <c r="J123" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K123" t="s">
         <v>466</v>
@@ -79030,7 +79030,7 @@
         <v>39</v>
       </c>
       <c r="J124" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K124" t="s">
         <v>469</v>
@@ -79065,7 +79065,7 @@
         <v>145</v>
       </c>
       <c r="J125" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K125" t="s">
         <v>472</v>
@@ -79100,7 +79100,7 @@
         <v>145</v>
       </c>
       <c r="J126" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K126" t="s">
         <v>477</v>
@@ -79132,7 +79132,7 @@
         <v>301</v>
       </c>
       <c r="J127" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K127" t="s">
         <v>480</v>
@@ -79164,7 +79164,7 @@
         <v>301</v>
       </c>
       <c r="J128" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K128" t="s">
         <v>480</v>
@@ -79202,7 +79202,7 @@
         <v>147</v>
       </c>
       <c r="J129" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K129" t="s">
         <v>349</v>
@@ -79240,7 +79240,7 @@
         <v>461</v>
       </c>
       <c r="J130" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K130" t="s">
         <v>462</v>
@@ -79278,7 +79278,7 @@
         <v>210</v>
       </c>
       <c r="J131" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K131" t="s">
         <v>259</v>
@@ -79316,7 +79316,7 @@
         <v>492</v>
       </c>
       <c r="J132" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K132" t="s">
         <v>444</v>
@@ -79354,7 +79354,7 @@
         <v>492</v>
       </c>
       <c r="J133" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K133" t="s">
         <v>495</v>
@@ -79392,7 +79392,7 @@
         <v>492</v>
       </c>
       <c r="J134" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K134" t="s">
         <v>495</v>
@@ -79427,7 +79427,7 @@
         <v>103</v>
       </c>
       <c r="J135" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K135" t="s">
         <v>499</v>
@@ -79465,7 +79465,7 @@
         <v>502</v>
       </c>
       <c r="J136" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K136" t="s">
         <v>263</v>
@@ -79500,7 +79500,7 @@
         <v>272</v>
       </c>
       <c r="J137" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K137" t="s">
         <v>503</v>
@@ -79535,7 +79535,7 @@
         <v>506</v>
       </c>
       <c r="J138" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K138" t="s">
         <v>507</v>
@@ -79570,7 +79570,7 @@
         <v>91</v>
       </c>
       <c r="J139" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K139" t="s">
         <v>511</v>
